--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -20722,7 +20722,7 @@
       </c>
       <c r="X46" s="26" t="inlineStr">
         <is>
-          <t>+12 signed</t>
+          <t>+12 signed (17 Mar → 20 Aug; over 156 day(s))</t>
         </is>
       </c>
     </row>
@@ -21877,17 +21877,17 @@
       </c>
       <c r="K56" s="27" t="inlineStr">
         <is>
-          <t>-44 signed</t>
+          <t>-44 signed (27 Feb → 25 Aug; over 179 day(s))</t>
         </is>
       </c>
       <c r="L56" s="28" t="inlineStr">
         <is>
-          <t>-38 signed</t>
+          <t>-38 signed (27 Feb → 25 Aug; over 179 day(s))</t>
         </is>
       </c>
       <c r="M56" s="29" t="inlineStr">
         <is>
-          <t>-34 signed</t>
+          <t>-34 signed (27 Feb → 25 Aug; over 179 day(s))</t>
         </is>
       </c>
       <c r="N56" s="19" t="inlineStr">
@@ -26258,7 +26258,7 @@
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>+3 signed</t>
+          <t>+3 signed (20 Aug → 11 Sep; over 22 day(s))</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
@@ -32629,9 +32629,9 @@
           <t>No observation</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>No change (11 Sep → 06 Oct; over 25 day(s))</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
@@ -32671,17 +32671,17 @@
       </c>
       <c r="K18" s="27" t="inlineStr">
         <is>
-          <t>+5 signed</t>
+          <t>+5 signed (25 Aug → 06 Oct; over 42 day(s))</t>
         </is>
       </c>
       <c r="L18" s="28" t="inlineStr">
         <is>
-          <t>+5 signed</t>
+          <t>+5 signed (25 Aug → 06 Oct; over 42 day(s))</t>
         </is>
       </c>
       <c r="M18" s="29" t="inlineStr">
         <is>
-          <t>+8 signed</t>
+          <t>+8 signed (25 Aug → 06 Oct; over 42 day(s))</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
@@ -32721,12 +32721,12 @@
       </c>
       <c r="U18" s="27" t="inlineStr">
         <is>
-          <t>+3 signed</t>
+          <t>+3 signed (25 Aug → 06 Oct; over 42 day(s))</t>
         </is>
       </c>
       <c r="V18" s="28" t="inlineStr">
         <is>
-          <t>-1 signed</t>
+          <t>-1 signed (25 Aug → 06 Oct; over 42 day(s))</t>
         </is>
       </c>
       <c r="W18" s="21" t="inlineStr">
@@ -32736,7 +32736,7 @@
       </c>
       <c r="X18" s="26" t="inlineStr">
         <is>
-          <t>+2 signed</t>
+          <t>+2 signed (20 Aug → 06 Oct; over 47 day(s))</t>
         </is>
       </c>
     </row>
@@ -45592,7 +45592,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>+17 signed</t>
+          <t>+17 signed (06 Oct → 27 Feb; over 144 day(s))</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
@@ -45682,12 +45682,12 @@
       </c>
       <c r="U60" s="27" t="inlineStr">
         <is>
-          <t>+40 signed</t>
-        </is>
-      </c>
-      <c r="V60" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+40 signed (06 Oct → 27 Feb; over 144 day(s))</t>
+        </is>
+      </c>
+      <c r="V60" s="28" t="inlineStr">
+        <is>
+          <t>No change (06 Oct → 27 Feb; over 144 day(s))</t>
         </is>
       </c>
       <c r="W60" s="21" t="inlineStr">
@@ -48061,72 +48061,72 @@
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>+9 signed</t>
+          <t>+9 signed (27 Feb → 08 Jun; over 101 day(s))</t>
         </is>
       </c>
       <c r="D22" s="26" t="inlineStr">
         <is>
-          <t>+4 signed</t>
+          <t>+4 signed (27 Feb → 08 Jun; over 101 day(s))</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Total changed — review</t>
+          <t>Total changed — review (06 Oct → 08 Jun; over 245 day(s))</t>
         </is>
       </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t>+1 signed</t>
+          <t>+1 signed (06 Oct → 08 Jun; over 245 day(s))</t>
         </is>
       </c>
       <c r="G22" s="28" t="inlineStr">
         <is>
-          <t>+9 signed</t>
+          <t>+9 signed (06 Oct → 08 Jun; over 245 day(s))</t>
         </is>
       </c>
       <c r="H22" s="28" t="inlineStr">
         <is>
-          <t>+11 signed</t>
+          <t>+11 signed (06 Oct → 08 Jun; over 245 day(s))</t>
         </is>
       </c>
       <c r="I22" s="29" t="inlineStr">
         <is>
-          <t>+4 signed</t>
+          <t>+4 signed (06 Oct → 08 Jun; over 245 day(s))</t>
         </is>
       </c>
       <c r="J22" s="26" t="inlineStr">
         <is>
-          <t>-10 signed</t>
+          <t>-10 signed (06 Oct → 08 Jun; over 245 day(s))</t>
         </is>
       </c>
       <c r="K22" s="27" t="inlineStr">
         <is>
-          <t>+40 signed</t>
+          <t>+40 signed (06 Oct → 08 Jun; over 245 day(s))</t>
         </is>
       </c>
       <c r="L22" s="28" t="inlineStr">
         <is>
-          <t>+33 signed</t>
+          <t>+33 signed (06 Oct → 08 Jun; over 245 day(s))</t>
         </is>
       </c>
       <c r="M22" s="29" t="inlineStr">
         <is>
-          <t>+26 signed</t>
+          <t>+26 signed (06 Oct → 08 Jun; over 245 day(s))</t>
         </is>
       </c>
       <c r="N22" s="27" t="inlineStr">
         <is>
-          <t>+14 signed</t>
+          <t>+14 signed (27 Feb → 08 Jun; over 466 day(s))</t>
         </is>
       </c>
       <c r="O22" s="28" t="inlineStr">
         <is>
-          <t>+34 signed</t>
+          <t>+34 signed (27 Feb → 08 Jun; over 466 day(s))</t>
         </is>
       </c>
       <c r="P22" s="29" t="inlineStr">
         <is>
-          <t>+54 signed</t>
+          <t>+54 signed (27 Feb → 08 Jun; over 466 day(s))</t>
         </is>
       </c>
       <c r="Q22" s="19" t="inlineStr">
@@ -48151,12 +48151,12 @@
       </c>
       <c r="U22" s="27" t="inlineStr">
         <is>
-          <t>+24 signed</t>
+          <t>+24 signed (27 Feb → 08 Jun; over 101 day(s))</t>
         </is>
       </c>
       <c r="V22" s="28" t="inlineStr">
         <is>
-          <t>+1 signed</t>
+          <t>+1 signed (27 Feb → 08 Jun; over 101 day(s))</t>
         </is>
       </c>
       <c r="W22" s="21" t="inlineStr">
@@ -48166,7 +48166,7 @@
       </c>
       <c r="X22" s="26" t="inlineStr">
         <is>
-          <t>+8 signed</t>
+          <t>+8 signed (06 Oct → 08 Jun; over 245 day(s))</t>
         </is>
       </c>
     </row>
@@ -56137,77 +56137,77 @@
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>+5 signed</t>
+          <t>+5 signed (08 Jun → 10 Jul; over 32 day(s))</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>+5 signed</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+5 signed (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="H26" s="28" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
         </is>
       </c>
       <c r="I26" s="29" t="inlineStr">
         <is>
-          <t>+1 signed</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="K26" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="N26" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+1 signed (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="K26" s="27" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="L26" s="28" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="M26" s="29" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="N26" s="27" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
         </is>
       </c>
       <c r="O26" s="28" t="inlineStr">
         <is>
-          <t>+5 signed</t>
+          <t>+5 signed (08 Jun → 10 Jul; over 32 day(s))</t>
         </is>
       </c>
       <c r="P26" s="29" t="inlineStr">
         <is>
-          <t>+18 signed</t>
+          <t>+18 signed (08 Jun → 10 Jul; over 32 day(s))</t>
         </is>
       </c>
       <c r="Q26" s="19" t="inlineStr">
@@ -56227,17 +56227,17 @@
       </c>
       <c r="T26" s="26" t="inlineStr">
         <is>
-          <t>+6 signed</t>
+          <t>+6 signed (08 Jun → 10 Jul; over 32 day(s))</t>
         </is>
       </c>
       <c r="U26" s="27" t="inlineStr">
         <is>
-          <t>+6 signed</t>
-        </is>
-      </c>
-      <c r="V26" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+6 signed (08 Jun → 10 Jul; over 32 day(s))</t>
+        </is>
+      </c>
+      <c r="V26" s="28" t="inlineStr">
+        <is>
+          <t>No change (08 Jun → 10 Jul; over 32 day(s))</t>
         </is>
       </c>
       <c r="W26" s="21" t="inlineStr">
@@ -56247,7 +56247,7 @@
       </c>
       <c r="X26" s="26" t="inlineStr">
         <is>
-          <t>+3 signed</t>
+          <t>+3 signed (08 Jun → 10 Jul; over 32 day(s))</t>
         </is>
       </c>
     </row>
@@ -64706,97 +64706,97 @@
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>+19 signed</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+19 signed (10 Jul → 13 Oct; over 95 day(s))</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>No change (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="D32" s="26" t="inlineStr">
         <is>
-          <t>+2 signed</t>
+          <t>+2 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="E32" s="26" t="inlineStr">
         <is>
-          <t>+1 signed</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="H32" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+1 signed (10 Jul → 13 Oct; over 95 day(s))</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="inlineStr">
+        <is>
+          <t>No change (10 Jul → 13 Oct; over 95 day(s))</t>
+        </is>
+      </c>
+      <c r="G32" s="28" t="inlineStr">
+        <is>
+          <t>No change (10 Jul → 13 Oct; over 95 day(s))</t>
+        </is>
+      </c>
+      <c r="H32" s="28" t="inlineStr">
+        <is>
+          <t>No change (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="I32" s="29" t="inlineStr">
         <is>
-          <t>+2 signed</t>
-        </is>
-      </c>
-      <c r="J32" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+2 signed (10 Jul → 13 Oct; over 95 day(s))</t>
+        </is>
+      </c>
+      <c r="J32" s="26" t="inlineStr">
+        <is>
+          <t>No change (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="K32" s="27" t="inlineStr">
         <is>
-          <t>+9 signed</t>
+          <t>+9 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="L32" s="28" t="inlineStr">
         <is>
-          <t>+3 signed</t>
+          <t>+3 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="M32" s="29" t="inlineStr">
         <is>
-          <t>+1 signed</t>
+          <t>+1 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="N32" s="27" t="inlineStr">
         <is>
-          <t>+6 signed</t>
+          <t>+6 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="O32" s="28" t="inlineStr">
         <is>
-          <t>+8 signed</t>
+          <t>+8 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="P32" s="29" t="inlineStr">
         <is>
-          <t>+9 signed</t>
+          <t>+9 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="Q32" s="27" t="inlineStr">
         <is>
-          <t>+13 signed</t>
+          <t>+13 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="R32" s="28" t="inlineStr">
         <is>
-          <t>+24 signed</t>
+          <t>+24 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="S32" s="29" t="inlineStr">
         <is>
-          <t>+11 signed</t>
+          <t>+11 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="T32" s="26" t="inlineStr">
         <is>
-          <t>+15 signed</t>
+          <t>+15 signed (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="U32" s="19" t="inlineStr">
@@ -64804,9 +64804,9 @@
           <t>No observation</t>
         </is>
       </c>
-      <c r="V32" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="V32" s="28" t="inlineStr">
+        <is>
+          <t>No change (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
       <c r="W32" s="21" t="inlineStr">
@@ -64814,9 +64814,9 @@
           <t>No prior record</t>
         </is>
       </c>
-      <c r="X32" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="X32" s="26" t="inlineStr">
+        <is>
+          <t>No change (10 Jul → 13 Oct; over 95 day(s))</t>
         </is>
       </c>
     </row>
@@ -65194,97 +65194,97 @@
       </c>
       <c r="B36" s="26" t="inlineStr">
         <is>
-          <t>+2 signed</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="J36" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="K36" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="M36" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="N36" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="O36" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="P36" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="Q36" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="R36" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+2 signed (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="G36" s="28" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="H36" s="28" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="I36" s="29" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="J36" s="26" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="K36" s="27" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="L36" s="28" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="M36" s="29" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="N36" s="27" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="O36" s="28" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="P36" s="29" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="Q36" s="27" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="R36" s="28" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
         </is>
       </c>
       <c r="S36" s="29" t="inlineStr">
         <is>
-          <t>+1 signed</t>
-        </is>
-      </c>
-      <c r="T36" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+1 signed (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="T36" s="26" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
         </is>
       </c>
       <c r="U36" s="19" t="inlineStr">
@@ -65292,19 +65292,19 @@
           <t>No observation</t>
         </is>
       </c>
-      <c r="V36" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="V36" s="28" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
         </is>
       </c>
       <c r="W36" s="29" t="inlineStr">
         <is>
-          <t>+1 signed</t>
-        </is>
-      </c>
-      <c r="X36" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+1 signed (13 Oct → 15 Oct; over 2 day(s))</t>
+        </is>
+      </c>
+      <c r="X36" s="26" t="inlineStr">
+        <is>
+          <t>No change (13 Oct → 15 Oct; over 2 day(s))</t>
         </is>
       </c>
     </row>
@@ -65436,99 +65436,99 @@
           <t>Daily Change</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="H38" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="J38" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="K38" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="L38" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="M38" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="N38" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="O38" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="P38" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="Q38" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="R38" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="S38" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="T38" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="G38" s="28" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="H38" s="28" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="I38" s="29" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="K38" s="27" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="L38" s="28" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="M38" s="29" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="N38" s="27" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="O38" s="28" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="P38" s="29" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="Q38" s="27" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="R38" s="28" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="S38" s="29" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="T38" s="26" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
         </is>
       </c>
       <c r="U38" s="19" t="inlineStr">
@@ -65536,19 +65536,19 @@
           <t>No observation</t>
         </is>
       </c>
-      <c r="V38" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="W38" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="X38" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="V38" s="28" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="W38" s="29" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="X38" s="26" t="inlineStr">
+        <is>
+          <t>No change (15 Oct → 16 Oct; over 1 day)</t>
         </is>
       </c>
     </row>
@@ -65680,99 +65680,99 @@
           <t>Daily Change</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
         </is>
       </c>
       <c r="C40" s="26" t="inlineStr">
         <is>
-          <t>+1 signed</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="G40" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="H40" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="I40" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="J40" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="K40" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="L40" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="M40" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="N40" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="O40" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="P40" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="Q40" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+1 signed (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="G40" s="28" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="I40" s="29" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="J40" s="26" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="K40" s="27" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="L40" s="28" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="M40" s="29" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="N40" s="27" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="O40" s="28" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="P40" s="29" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="Q40" s="27" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
         </is>
       </c>
       <c r="R40" s="28" t="inlineStr">
         <is>
-          <t>+2 signed</t>
+          <t>+2 signed (16 Oct → 17 Oct; over 1 day)</t>
         </is>
       </c>
       <c r="S40" s="29" t="inlineStr">
         <is>
-          <t>+1 signed</t>
-        </is>
-      </c>
-      <c r="T40" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+          <t>+1 signed (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="T40" s="26" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
         </is>
       </c>
       <c r="U40" s="19" t="inlineStr">
@@ -65780,19 +65780,19 @@
           <t>No observation</t>
         </is>
       </c>
-      <c r="V40" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="W40" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="X40" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="V40" s="28" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="W40" s="29" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="X40" s="26" t="inlineStr">
+        <is>
+          <t>No change (16 Oct → 17 Oct; over 1 day)</t>
         </is>
       </c>
     </row>
@@ -65924,99 +65924,99 @@
           <t>Daily Change</t>
         </is>
       </c>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="H42" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="I42" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="J42" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="K42" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="L42" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="M42" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="N42" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="O42" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="P42" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="Q42" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="R42" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="S42" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="T42" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="G42" s="28" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="H42" s="28" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="I42" s="29" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="J42" s="26" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="K42" s="27" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="L42" s="28" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="M42" s="29" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="N42" s="27" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="O42" s="28" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="P42" s="29" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="Q42" s="27" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="R42" s="28" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="S42" s="29" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="T42" s="26" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
         </is>
       </c>
       <c r="U42" s="19" t="inlineStr">
@@ -66024,19 +66024,19 @@
           <t>No observation</t>
         </is>
       </c>
-      <c r="V42" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="W42" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="X42" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="V42" s="28" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="W42" s="29" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="X42" s="26" t="inlineStr">
+        <is>
+          <t>No change (17 Oct → 18 Oct; over 1 day)</t>
         </is>
       </c>
     </row>
@@ -66168,99 +66168,99 @@
           <t>Daily Change</t>
         </is>
       </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="F44" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="G44" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="H44" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="I44" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="J44" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="K44" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="L44" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="M44" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="N44" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="O44" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="P44" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="Q44" s="19" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="R44" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="S44" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="T44" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="G44" s="28" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="H44" s="28" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="I44" s="29" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="J44" s="26" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="K44" s="27" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="L44" s="28" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="M44" s="29" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="N44" s="27" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="O44" s="28" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="P44" s="29" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="Q44" s="27" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="R44" s="28" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="S44" s="29" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="T44" s="26" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
         </is>
       </c>
       <c r="U44" s="19" t="inlineStr">
@@ -66268,19 +66268,19 @@
           <t>No observation</t>
         </is>
       </c>
-      <c r="V44" s="20" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="W44" s="21" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-      <c r="X44" s="18" t="inlineStr">
-        <is>
-          <t>No change</t>
+      <c r="V44" s="28" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="W44" s="29" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
+        </is>
+      </c>
+      <c r="X44" s="26" t="inlineStr">
+        <is>
+          <t>No change (18 Oct → 19 Oct; over 1 day)</t>
         </is>
       </c>
     </row>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Jun 2026'!$1:$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Jul 2026'!$A$6:$AB$68</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Jul 2026'!$1:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Oct 2026'!$A$6:$AB$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Oct 2026'!$A$6:$AB$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Oct 2026'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -62966,7 +62966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -68640,8 +68640,292 @@
         </is>
       </c>
     </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="J45" s="15" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="K45" s="15" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="L45" s="15" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="N45" s="13" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="O45" s="14" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="P45" s="15" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="Q45" s="16" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="R45" s="14" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="S45" s="15" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="T45" s="16" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="U45" s="14" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="V45" s="15" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="W45" s="16" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="X45" s="13" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="Y45" s="14" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="Z45" s="15" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="AA45" s="16" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+      <c r="AB45" s="13" t="inlineStr">
+        <is>
+          <t>No signed observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="27" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>Daily Change</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="J46" s="20" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="K46" s="20" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="M46" s="21" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="N46" s="18" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="O46" s="19" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="P46" s="20" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="Q46" s="21" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="R46" s="19" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="S46" s="20" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="T46" s="21" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="U46" s="19" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="V46" s="20" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="W46" s="21" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="X46" s="18" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="Y46" s="19" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="Z46" s="20" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="AA46" s="21" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+      <c r="AB46" s="18" t="inlineStr">
+        <is>
+          <t>No observation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:AB44"/>
+  <autoFilter ref="A6:AB46"/>
   <mergeCells count="8">
     <mergeCell ref="A2:AB2"/>
     <mergeCell ref="O5:Q5"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -68646,24 +68646,24 @@
           <t>20 Oct 2026 · Sales Status</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>44% Signed (21/48 units)</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -68676,24 +68676,24 @@
           <t>No signed observation</t>
         </is>
       </c>
-      <c r="H45" s="15" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="J45" s="15" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="K45" s="15" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
+      <c r="H45" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="I45" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="inlineStr">
+        <is>
+          <t>96% Signed (24/25 units)</t>
+        </is>
+      </c>
+      <c r="K45" s="25" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
         </is>
       </c>
       <c r="L45" s="15" t="inlineStr">
@@ -68706,59 +68706,59 @@
           <t>No signed observation</t>
         </is>
       </c>
-      <c r="N45" s="13" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="O45" s="14" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="P45" s="15" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="Q45" s="16" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="R45" s="14" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="S45" s="15" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="T45" s="16" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="U45" s="14" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="V45" s="15" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="W45" s="16" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="X45" s="13" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
+      <c r="N45" s="22" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="O45" s="24" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="P45" s="25" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="Q45" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="R45" s="24" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="S45" s="25" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="T45" s="26" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="U45" s="24" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="V45" s="25" t="inlineStr">
+        <is>
+          <t>76% Signed (65/85 units)</t>
+        </is>
+      </c>
+      <c r="W45" s="26" t="inlineStr">
+        <is>
+          <t>24% Signed (24/102 units)</t>
+        </is>
+      </c>
+      <c r="X45" s="22" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
         </is>
       </c>
       <c r="Y45" s="14" t="inlineStr">
@@ -68766,19 +68766,19 @@
           <t>No signed observation</t>
         </is>
       </c>
-      <c r="Z45" s="15" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="AA45" s="16" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
-        </is>
-      </c>
-      <c r="AB45" s="13" t="inlineStr">
-        <is>
-          <t>No signed observation</t>
+      <c r="Z45" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="AA45" s="26" t="inlineStr">
+        <is>
+          <t>52% Signed (161/308 units)</t>
+        </is>
+      </c>
+      <c r="AB45" s="22" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
         </is>
       </c>
     </row>
@@ -68790,22 +68790,22 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="D46" s="18" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
@@ -68820,22 +68820,22 @@
       </c>
       <c r="H46" s="20" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="J46" s="20" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="K46" s="20" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="L46" s="20" t="inlineStr">
@@ -68850,57 +68850,57 @@
       </c>
       <c r="N46" s="18" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="O46" s="19" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="P46" s="20" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="Q46" s="21" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="R46" s="19" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="S46" s="20" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="T46" s="21" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="U46" s="19" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="V46" s="20" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="W46" s="21" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="X46" s="18" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="Y46" s="19" t="inlineStr">
@@ -68910,17 +68910,17 @@
       </c>
       <c r="Z46" s="20" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="AA46" s="21" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="AB46" s="18" t="inlineStr">
         <is>
-          <t>No observation</t>
+          <t>No change</t>
         </is>
       </c>
     </row>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -5331,7 +5331,7 @@
       </c>
       <c r="V42" s="32" t="inlineStr">
         <is>
-          <t>Total changed — review scope/release</t>
+          <t>⚠ Scope changed (189 → 308); +6 signed; -29.5 pp</t>
         </is>
       </c>
       <c r="W42" s="19" t="inlineStr">

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$67</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W64"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7606,8 +7606,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E65" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F65" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G65" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H65" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I65" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J65" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K65" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L65" s="26" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="M65" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N65" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O65" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P65" s="27" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="Q65" s="25" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="R65" s="26" t="inlineStr">
+        <is>
+          <t>76% Signed (65/85 units)</t>
+        </is>
+      </c>
+      <c r="S65" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (25/102 units)</t>
+        </is>
+      </c>
+      <c r="T65" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U65" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V65" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W65" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="27" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D66" s="28" t="inlineStr">
+        <is>
+          <t>+1 signed</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G66" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H66" s="31" t="inlineStr">
+        <is>
+          <t>+1 signed</t>
+        </is>
+      </c>
+      <c r="I66" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K66" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L66" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="M66" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N66" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O66" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P66" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="Q66" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="R66" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="S66" s="29" t="inlineStr">
+        <is>
+          <t>+1 signed</t>
+        </is>
+      </c>
+      <c r="T66" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U66" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V66" s="32" t="inlineStr">
+        <is>
+          <t>⚠ Scope changed (308 → 346); 0 signed change; -5.7 pp</t>
+        </is>
+      </c>
+      <c r="W66" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W64"/>
+  <autoFilter ref="A3:W67"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$70</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:W70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7913,8 +7913,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F68" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G68" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H68" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I68" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J68" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K68" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L68" s="26" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="M68" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N68" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O68" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P68" s="27" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="Q68" s="25" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="R68" s="26" t="inlineStr">
+        <is>
+          <t>78% Signed (66/85 units)</t>
+        </is>
+      </c>
+      <c r="S68" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (25/102 units)</t>
+        </is>
+      </c>
+      <c r="T68" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U68" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V68" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W68" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="27" customHeight="1">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H69" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="I69" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K69" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L69" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="M69" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N69" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O69" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P69" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="Q69" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="R69" s="31" t="inlineStr">
+        <is>
+          <t>+1 signed</t>
+        </is>
+      </c>
+      <c r="S69" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="T69" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U69" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V69" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="W69" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W67"/>
+  <autoFilter ref="A3:W70"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$73</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W70"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8220,8 +8220,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F71" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G71" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H71" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I71" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J71" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K71" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L71" s="26" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="M71" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N71" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O71" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P71" s="27" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="Q71" s="25" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="R71" s="26" t="inlineStr">
+        <is>
+          <t>78% Signed (66/85 units)</t>
+        </is>
+      </c>
+      <c r="S71" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (25/102 units)</t>
+        </is>
+      </c>
+      <c r="T71" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U71" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V71" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W71" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="27" customHeight="1">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="E72" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G72" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H72" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="I72" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J72" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K72" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L72" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="M72" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N72" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O72" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P72" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="Q72" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="R72" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="S72" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="T72" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U72" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V72" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="W72" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W70"/>
+  <autoFilter ref="A3:W73"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8527,8 +8527,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="74" ht="32" customHeight="1">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F74" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G74" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H74" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I74" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J74" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K74" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L74" s="26" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="M74" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N74" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O74" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P74" s="27" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="Q74" s="25" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="R74" s="26" t="inlineStr">
+        <is>
+          <t>79% Signed (67/85 units)</t>
+        </is>
+      </c>
+      <c r="S74" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (26/102 units)</t>
+        </is>
+      </c>
+      <c r="T74" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U74" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V74" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W74" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="27" customHeight="1">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F75" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G75" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H75" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="I75" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J75" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K75" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L75" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="M75" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N75" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O75" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P75" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="Q75" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="R75" s="31" t="inlineStr">
+        <is>
+          <t>+1 signed</t>
+        </is>
+      </c>
+      <c r="S75" s="29" t="inlineStr">
+        <is>
+          <t>+1 signed</t>
+        </is>
+      </c>
+      <c r="T75" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U75" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V75" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="W75" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W76" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W73"/>
+  <autoFilter ref="A3:W76"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$79</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W76"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8834,8 +8834,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F77" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G77" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H77" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I77" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J77" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K77" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L77" s="26" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="M77" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N77" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O77" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P77" s="27" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="Q77" s="25" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="R77" s="26" t="inlineStr">
+        <is>
+          <t>79% Signed (67/85 units)</t>
+        </is>
+      </c>
+      <c r="S77" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (26/102 units)</t>
+        </is>
+      </c>
+      <c r="T77" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U77" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V77" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W77" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="27" customHeight="1">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="E78" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G78" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H78" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="I78" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J78" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K78" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L78" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="M78" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N78" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O78" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P78" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="Q78" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="R78" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="S78" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="T78" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U78" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V78" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="W78" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W79" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W76"/>
+  <autoFilter ref="A3:W79"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$82</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:W82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9141,8 +9141,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C80" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F80" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G80" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H80" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J80" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K80" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L80" s="26" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="M80" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N80" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O80" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P80" s="27" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="Q80" s="25" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="R80" s="26" t="inlineStr">
+        <is>
+          <t>79% Signed (67/85 units)</t>
+        </is>
+      </c>
+      <c r="S80" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (26/102 units)</t>
+        </is>
+      </c>
+      <c r="T80" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U80" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V80" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W80" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="27" customHeight="1">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F81" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G81" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H81" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="I81" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K81" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L81" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="M81" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N81" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O81" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P81" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="Q81" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="R81" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="S81" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="T81" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U81" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V81" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="W81" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W82" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W79"/>
+  <autoFilter ref="A3:W82"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$85</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W82"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9448,8 +9448,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F83" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G83" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H83" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I83" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K83" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L83" s="26" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="M83" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N83" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O83" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P83" s="27" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="Q83" s="25" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="R83" s="26" t="inlineStr">
+        <is>
+          <t>79% Signed (67/85 units)</t>
+        </is>
+      </c>
+      <c r="S83" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (26/102 units)</t>
+        </is>
+      </c>
+      <c r="T83" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U83" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V83" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W83" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="27" customHeight="1">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F84" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G84" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H84" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="I84" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J84" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K84" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L84" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="M84" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N84" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O84" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P84" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="Q84" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="R84" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="S84" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="T84" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U84" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V84" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="W84" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W85" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W82"/>
+  <autoFilter ref="A3:W85"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$88</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W85"/>
+  <dimension ref="A1:W88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9755,8 +9755,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E86" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F86" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G86" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H86" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I86" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J86" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K86" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L86" s="26" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="M86" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N86" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O86" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P86" s="27" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="Q86" s="25" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="R86" s="26" t="inlineStr">
+        <is>
+          <t>79% Signed (67/85 units)</t>
+        </is>
+      </c>
+      <c r="S86" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (26/102 units)</t>
+        </is>
+      </c>
+      <c r="T86" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U86" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V86" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W86" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="27" customHeight="1">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="E87" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F87" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G87" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H87" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="I87" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J87" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K87" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L87" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="M87" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N87" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O87" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P87" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="Q87" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="R87" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="S87" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="T87" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U87" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V87" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="W87" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P88" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W88" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W85"/>
+  <autoFilter ref="A3:W88"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W88"/>
+  <dimension ref="A1:W91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10062,8 +10062,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F89" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G89" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H89" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I89" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J89" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K89" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L89" s="26" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="M89" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N89" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O89" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P89" s="27" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="Q89" s="25" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="R89" s="26" t="inlineStr">
+        <is>
+          <t>79% Signed (67/85 units)</t>
+        </is>
+      </c>
+      <c r="S89" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (26/102 units)</t>
+        </is>
+      </c>
+      <c r="T89" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U89" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V89" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W89" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="27" customHeight="1">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D90" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="E90" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F90" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G90" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H90" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="I90" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J90" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K90" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L90" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="M90" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N90" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O90" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P90" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="Q90" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="R90" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="S90" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="T90" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U90" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V90" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="W90" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W91" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W88"/>
+  <autoFilter ref="A3:W91"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$94</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W91"/>
+  <dimension ref="A1:W94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10369,8 +10369,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B92" s="24" t="inlineStr">
+        <is>
+          <t>91% Signed (74/81 units)</t>
+        </is>
+      </c>
+      <c r="C92" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E92" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F92" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G92" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H92" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I92" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J92" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K92" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L92" s="26" t="inlineStr">
+        <is>
+          <t>97% Signed (134/138 units)</t>
+        </is>
+      </c>
+      <c r="M92" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N92" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O92" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P92" s="27" t="inlineStr">
+        <is>
+          <t>94% Signed (98/104 units)</t>
+        </is>
+      </c>
+      <c r="Q92" s="25" t="inlineStr">
+        <is>
+          <t>66% Signed (29/44 units)</t>
+        </is>
+      </c>
+      <c r="R92" s="26" t="inlineStr">
+        <is>
+          <t>79% Signed (67/85 units)</t>
+        </is>
+      </c>
+      <c r="S92" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (26/102 units)</t>
+        </is>
+      </c>
+      <c r="T92" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U92" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V92" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W92" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="27" customHeight="1">
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G93" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H93" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="I93" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J93" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K93" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L93" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="M93" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N93" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O93" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P93" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="Q93" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="R93" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="S93" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="T93" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U93" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V93" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="W93" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q94" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S94" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W94" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W91"/>
+  <autoFilter ref="A3:W94"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>

--- a/Broga_Daily_Tracking.xlsx
+++ b/Broga_Daily_Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oct 2026'!$A$3:$W$97</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Oct 2026'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:W97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10676,8 +10676,315 @@
         <v>1</v>
       </c>
     </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>31 Oct 2026 · Sales Status</t>
+        </is>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
+        <is>
+          <t>94% Signed (76/81 units)</t>
+        </is>
+      </c>
+      <c r="C95" s="24" t="inlineStr">
+        <is>
+          <t>61% Signed (69/113 units)</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>46% Signed (22/48 units)</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>63% Signed (71/113 units)</t>
+        </is>
+      </c>
+      <c r="F95" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (46/46 units)</t>
+        </is>
+      </c>
+      <c r="G95" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (56/56 units)</t>
+        </is>
+      </c>
+      <c r="H95" s="26" t="inlineStr">
+        <is>
+          <t>100% Signed (25/25 units)</t>
+        </is>
+      </c>
+      <c r="I95" s="27" t="inlineStr">
+        <is>
+          <t>40% Signed (10/25 units)</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>78% Signed (77/99 units)</t>
+        </is>
+      </c>
+      <c r="K95" s="25" t="inlineStr">
+        <is>
+          <t>100% Signed (111/111 units)</t>
+        </is>
+      </c>
+      <c r="L95" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (135/138 units)</t>
+        </is>
+      </c>
+      <c r="M95" s="27" t="inlineStr">
+        <is>
+          <t>98% Signed (79/81 units)</t>
+        </is>
+      </c>
+      <c r="N95" s="25" t="inlineStr">
+        <is>
+          <t>88% Signed (23/26 units)</t>
+        </is>
+      </c>
+      <c r="O95" s="26" t="inlineStr">
+        <is>
+          <t>98% Signed (124/126 units)</t>
+        </is>
+      </c>
+      <c r="P95" s="27" t="inlineStr">
+        <is>
+          <t>95% Signed (99/104 units)</t>
+        </is>
+      </c>
+      <c r="Q95" s="25" t="inlineStr">
+        <is>
+          <t>70% Signed (31/44 units)</t>
+        </is>
+      </c>
+      <c r="R95" s="26" t="inlineStr">
+        <is>
+          <t>80% Signed (68/85 units)</t>
+        </is>
+      </c>
+      <c r="S95" s="27" t="inlineStr">
+        <is>
+          <t>25% Signed (26/102 units)</t>
+        </is>
+      </c>
+      <c r="T95" s="24" t="inlineStr">
+        <is>
+          <t>33% Signed (45/136 units)</t>
+        </is>
+      </c>
+      <c r="U95" s="25" t="inlineStr">
+        <is>
+          <t>4% Signed (1/27 units)</t>
+        </is>
+      </c>
+      <c r="V95" s="27" t="inlineStr">
+        <is>
+          <t>47% Signed (161/346 units)</t>
+        </is>
+      </c>
+      <c r="W95" s="24" t="inlineStr">
+        <is>
+          <t>23% Signed (34/149 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="27" customHeight="1">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>Change vs Previous Observation</t>
+        </is>
+      </c>
+      <c r="B96" s="28" t="inlineStr">
+        <is>
+          <t>+2 signed</t>
+        </is>
+      </c>
+      <c r="C96" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="D96" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="E96" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="F96" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="G96" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="I96" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="J96" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="K96" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="L96" s="31" t="inlineStr">
+        <is>
+          <t>+1 signed</t>
+        </is>
+      </c>
+      <c r="M96" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="N96" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="O96" s="21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="P96" s="29" t="inlineStr">
+        <is>
+          <t>+1 signed</t>
+        </is>
+      </c>
+      <c r="Q96" s="30" t="inlineStr">
+        <is>
+          <t>+2 signed</t>
+        </is>
+      </c>
+      <c r="R96" s="31" t="inlineStr">
+        <is>
+          <t>+1 signed</t>
+        </is>
+      </c>
+      <c r="S96" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="T96" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="U96" s="20" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="V96" s="22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+      <c r="W96" s="19" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="23" t="inlineStr">
+        <is>
+          <t>Days Since Previous Observation</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P97" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q97" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W97" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:W94"/>
+  <autoFilter ref="A3:W97"/>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A1:W1"/>
